--- a/ペアプログラミング.xlsx
+++ b/ペアプログラミング.xlsx
@@ -5,20 +5,20 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fukuyama\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fukuyama\Documents\GitHub\Team1_Pair_Programming\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BE934319-2FE8-4770-A7AB-B5065F1C003F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F4BA1B8C-8B19-4430-B8C7-B92779599608}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-5580" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{B81832F0-03C7-4738-AFAD-96C86A7EDCD9}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{B81832F0-03C7-4738-AFAD-96C86A7EDCD9}"/>
   </bookViews>
   <sheets>
     <sheet name="役割分担" sheetId="2" r:id="rId1"/>
     <sheet name="データ" sheetId="1" r:id="rId2"/>
     <sheet name="画面" sheetId="6" r:id="rId3"/>
-    <sheet name="Sheet5" sheetId="5" r:id="rId4"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId5"/>
-    <sheet name="Sheet4" sheetId="4" r:id="rId6"/>
+    <sheet name="データ設計" sheetId="4" r:id="rId4"/>
+    <sheet name="Nlog" sheetId="3" r:id="rId5"/>
+    <sheet name="Sheet5" sheetId="5" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="66">
   <si>
     <t>合計金額</t>
     <rPh sb="0" eb="4">
@@ -128,14 +128,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>TotalCost</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Purchase Date</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>プロパティ名</t>
     <rPh sb="5" eb="6">
       <t>メイ</t>
@@ -147,10 +139,6 @@
     <rPh sb="3" eb="4">
       <t>メイ</t>
     </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Prodacts</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -694,6 +682,33 @@
     <rPh sb="16" eb="18">
       <t>ソウサ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>個数</t>
+    <rPh sb="0" eb="2">
+      <t>コスウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Products</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>PurchaseDate</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ProductQuantity</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ProductTotalCost</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -764,7 +779,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -775,12 +790,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
@@ -1127,30 +1136,30 @@
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="7"/>
+      <c r="D2" s="5"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="7"/>
+      <c r="D3" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -1171,60 +1180,68 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="7"/>
+      <c r="B2" s="5"/>
       <c r="C2" t="s">
         <v>12</v>
       </c>
       <c r="E2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A3" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B3" s="5"/>
+      <c r="C3" t="s">
+        <v>64</v>
+      </c>
+      <c r="E3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A4" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="D4" s="5"/>
+      <c r="E4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A5" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="5"/>
+      <c r="C5" t="s">
+        <v>63</v>
+      </c>
+      <c r="E5" t="s">
         <v>17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A3" s="7"/>
-      <c r="B3" s="7"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A4" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" s="7"/>
-      <c r="E4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A5" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="7"/>
-      <c r="C5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5" t="s">
-        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -1252,187 +1269,187 @@
   <sheetData>
     <row r="1" spans="1:3" ht="22.2" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="72" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="22.2" x14ac:dyDescent="0.45">
       <c r="A6" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="72" x14ac:dyDescent="0.45">
       <c r="A8" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>28</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="36" x14ac:dyDescent="0.45">
       <c r="A9" s="2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B9" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>30</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="108" x14ac:dyDescent="0.45">
       <c r="A10" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="108" x14ac:dyDescent="0.45">
       <c r="A11" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="36" x14ac:dyDescent="0.45">
       <c r="A12" s="2" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="54" x14ac:dyDescent="0.45">
-      <c r="A13" s="4" t="s">
-        <v>52</v>
+      <c r="A13" s="2" t="s">
+        <v>49</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="22.2" x14ac:dyDescent="0.45">
       <c r="A15" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A16" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="72" x14ac:dyDescent="0.45">
-      <c r="A17" s="4" t="s">
+      <c r="A17" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B17" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="C17" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="252" x14ac:dyDescent="0.45">
+      <c r="A18" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B18" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="C18" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="72" x14ac:dyDescent="0.45">
+      <c r="A19" s="2" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" ht="252" x14ac:dyDescent="0.45">
-      <c r="A18" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" ht="72" x14ac:dyDescent="0.45">
-      <c r="A19" s="4" t="s">
-        <v>52</v>
-      </c>
       <c r="B19" s="3" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="22.2" x14ac:dyDescent="0.45">
       <c r="A22" s="1" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A23" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="72" x14ac:dyDescent="0.45">
-      <c r="A24" s="4" t="s">
-        <v>23</v>
+      <c r="A24" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -1442,21 +1459,40 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14116DB6-C253-424F-A6F5-C79073A4DB09}">
-  <dimension ref="A1:A2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5B61B72-1F59-43FF-8717-72DCDA6711B3}">
+  <dimension ref="A1:D3"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
-        <v>57</v>
-      </c>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A1" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A2" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A3" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="B3" s="5"/>
+      <c r="C3" s="5"/>
+      <c r="D3" s="5"/>
     </row>
   </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A3:D3"/>
+  </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1484,23 +1520,18 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5B61B72-1F59-43FF-8717-72DCDA6711B3}">
-  <dimension ref="A1:A3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14116DB6-C253-424F-A6F5-C79073A4DB09}">
+  <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>

--- a/ペアプログラミング.xlsx
+++ b/ペアプログラミング.xlsx
@@ -8,17 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\fukuyama\Documents\GitHub\Team1_Pair_Programming\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F4BA1B8C-8B19-4430-B8C7-B92779599608}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E6BD87D0-B53D-4D6E-BD6A-613122DFA1CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{B81832F0-03C7-4738-AFAD-96C86A7EDCD9}"/>
+    <workbookView xWindow="28680" yWindow="-5580" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{B81832F0-03C7-4738-AFAD-96C86A7EDCD9}"/>
   </bookViews>
   <sheets>
     <sheet name="役割分担" sheetId="2" r:id="rId1"/>
     <sheet name="データ" sheetId="1" r:id="rId2"/>
     <sheet name="画面" sheetId="6" r:id="rId3"/>
-    <sheet name="データ設計" sheetId="4" r:id="rId4"/>
-    <sheet name="Nlog" sheetId="3" r:id="rId5"/>
-    <sheet name="Sheet5" sheetId="5" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="59">
   <si>
     <t>合計金額</t>
     <rPh sb="0" eb="4">
@@ -95,28 +92,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ログ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Nログのテキストファイル</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>プロパティとリストで設計</t>
-    <rPh sb="10" eb="12">
-      <t>セッケイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>データ設計（モックデータ）</t>
-    <rPh sb="3" eb="5">
-      <t>セッケイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>商品名</t>
     <rPh sb="0" eb="3">
       <t>ショウヒンメイ</t>
@@ -201,13 +176,6 @@
   </si>
   <si>
     <t>左記のような初期表示</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>商品を選択してください
-()A
-(選択中)B
-()C</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -535,37 +503,6 @@
     </rPh>
     <rPh sb="12" eb="13">
       <t>モド</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>履歴表示
-(*)合計金額の降順
-( )日付順
-( )システム選択画面へ</t>
-    <rPh sb="0" eb="4">
-      <t>リレキヒョウジ</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>ゴウケイ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>キンガク</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>コウジュン</t>
-    </rPh>
-    <rPh sb="19" eb="21">
-      <t>ヒヅケ</t>
-    </rPh>
-    <rPh sb="21" eb="22">
-      <t>ジュン</t>
-    </rPh>
-    <rPh sb="30" eb="32">
-      <t>センタク</t>
-    </rPh>
-    <rPh sb="32" eb="34">
-      <t>ガメン</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -609,14 +546,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>データ取得機能（GET）</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>HTTPメソッド：GET</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>アプリ終了</t>
     <rPh sb="3" eb="5">
       <t>シュウリョウ</t>
@@ -675,16 +604,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>もらったデータをクライアント側で操作</t>
-    <rPh sb="14" eb="15">
-      <t>ガワ</t>
-    </rPh>
-    <rPh sb="16" eb="18">
-      <t>ソウサ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>個数</t>
     <rPh sb="0" eb="2">
       <t>コスウ</t>
@@ -708,7 +627,45 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>ProductTotalCost</t>
+    <t>TotalCost</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>履歴表示
+(*)合計金額の昇順
+( )日付順
+( )システム選択画面へ</t>
+    <rPh sb="0" eb="4">
+      <t>リレキヒョウジ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ゴウケイ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>キンガク</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ショウジュン</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ヒヅケ</t>
+    </rPh>
+    <rPh sb="21" eb="22">
+      <t>ジュン</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>センタク</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>ガメン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>商品を選択してください
+()A
+(*)B
+()C</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1180,43 +1137,43 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A2" s="5" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B2" s="5"/>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F2" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A3" s="5" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="B3" s="5"/>
       <c r="C3" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="E3" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.45">
@@ -1225,11 +1182,11 @@
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="D4" s="5"/>
       <c r="E4" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.45">
@@ -1238,10 +1195,10 @@
       </c>
       <c r="B5" s="5"/>
       <c r="C5" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="E5" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -1269,269 +1226,187 @@
   <sheetData>
     <row r="1" spans="1:3" ht="22.2" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="72" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="22.2" x14ac:dyDescent="0.45">
       <c r="A6" s="1" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="72" x14ac:dyDescent="0.45">
       <c r="A8" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>26</v>
+        <v>58</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="36" x14ac:dyDescent="0.45">
       <c r="A9" s="2" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="108" x14ac:dyDescent="0.45">
       <c r="A10" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="108" x14ac:dyDescent="0.45">
       <c r="A11" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>33</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="36" x14ac:dyDescent="0.45">
       <c r="A12" s="2" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="54" x14ac:dyDescent="0.45">
       <c r="A13" s="2" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="22.2" x14ac:dyDescent="0.45">
       <c r="A15" s="1" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A16" s="2" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="72" x14ac:dyDescent="0.45">
       <c r="A17" s="2" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="252" x14ac:dyDescent="0.45">
       <c r="A18" s="3" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="72" x14ac:dyDescent="0.45">
       <c r="A19" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B19" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>57</v>
-      </c>
       <c r="C19" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="22.2" x14ac:dyDescent="0.45">
       <c r="A22" s="1" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A23" s="2" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="72" x14ac:dyDescent="0.45">
       <c r="A24" s="2" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>58</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5B61B72-1F59-43FF-8717-72DCDA6711B3}">
-  <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A1" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A2" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="5"/>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A3" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="B3" s="5"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-    </row>
-  </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A3:D3"/>
-  </mergeCells>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F227B0F3-EB1A-40D5-BC07-E5A2F7E1D683}">
-  <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14116DB6-C253-424F-A6F5-C79073A4DB09}">
-  <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
